--- a/output/traffic_report.xlsx
+++ b/output/traffic_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,10 +465,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.033333333333333</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -477,29 +477,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>车辆过多 (25辆 &gt; 15辆)</t>
+          <t>拥堵：车辆过多 (26辆 &gt; 25辆)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>2.002877786541077</v>
+        <v>1.166419254892398</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (25辆 &gt; 15辆)</t>
+          <t>🚨 交通拥堵警报！拥堵：车辆过多 (26辆 &gt; 25辆)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2.066666666666667</v>
+        <v>6.066666666666666</v>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -508,29 +508,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>车辆过多 (22辆 &gt; 15辆)</t>
+          <t>拥堵：22辆车，车速过慢 (1.1像素/帧)</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>1.107963702533058</v>
+        <v>1.098301604604174</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (22辆 &gt; 15辆)</t>
+          <t>🚨 交通拥堵警报！拥堵：22辆车，车速过慢 (1.1像素/帧)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3.1</v>
+        <v>9.1</v>
       </c>
       <c r="B4" t="n">
-        <v>93</v>
+        <v>273</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -539,60 +539,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>车辆过多 (24辆 &gt; 15辆)</t>
+          <t>拥堵：20辆车，车速过慢 (1.6像素/帧)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>1.068374430199477</v>
+        <v>1.562283505285556</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (24辆 &gt; 15辆)</t>
+          <t>🚨 交通拥堵警报！拥堵：20辆车，车速过慢 (1.6像素/帧)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4.133333333333334</v>
+        <v>10.73333333333333</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>322</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>车辆过多 (22辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>22</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.823354926711104</v>
-      </c>
+          <t>congestion_end</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>7.7</v>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (22辆 &gt; 15辆)</t>
+          <t>✅ 拥堵解除，持续了 7.7 秒</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5.166666666666667</v>
+        <v>12.13333333333333</v>
       </c>
       <c r="B6" t="n">
-        <v>155</v>
+        <v>364</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -601,29 +595,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>车辆过多 (20辆 &gt; 15辆)</t>
+          <t>拥堵：20辆车，车速过慢 (1.5像素/帧)</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8035533905932738</v>
+        <v>1.517747059841649</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (20辆 &gt; 15辆)</t>
+          <t>🚨 交通拥堵警报！拥堵：20辆车，车速过慢 (1.5像素/帧)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6.2</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -632,29 +626,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>车辆过多 (23辆 &gt; 15辆)</t>
+          <t>拥堵：22辆车，车速过慢 (0.8像素/帧)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>1.407155333147189</v>
+        <v>0.8370346751529457</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (23辆 &gt; 15辆)</t>
+          <t>🚨 交通拥堵警报！拥堵：22辆车，车速过慢 (0.8像素/帧)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7.233333333333333</v>
+        <v>18.2</v>
       </c>
       <c r="B8" t="n">
-        <v>217</v>
+        <v>546</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -663,29 +657,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>车辆过多 (22辆 &gt; 15辆)</t>
+          <t>拥堵：22辆车，车速过慢 (1.4像素/帧)</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>22</v>
       </c>
       <c r="F8" t="n">
-        <v>1.311451488638053</v>
+        <v>1.389225845668279</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (22辆 &gt; 15辆)</t>
+          <t>🚨 交通拥堵警报！拥堵：22辆车，车速过慢 (1.4像素/帧)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8.266666666666667</v>
+        <v>21.23333333333333</v>
       </c>
       <c r="B9" t="n">
-        <v>248</v>
+        <v>637</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -694,29 +688,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>车辆过多 (24辆 &gt; 15辆)</t>
+          <t>拥堵：19辆车，车速过慢 (1.4像素/帧)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
-        <v>1.585186175139323</v>
+        <v>1.390839142205651</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (24辆 &gt; 15辆)</t>
+          <t>🚨 交通拥堵警报！拥堵：19辆车，车速过慢 (1.4像素/帧)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9.300000000000001</v>
+        <v>24.26666666666667</v>
       </c>
       <c r="B10" t="n">
-        <v>279</v>
+        <v>728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -725,29 +719,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>车辆过多 (22辆 &gt; 15辆)</t>
+          <t>拥堵：20辆车，车速过慢 (1.2像素/帧)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>1.043096459734215</v>
+        <v>1.186067467586918</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (22辆 &gt; 15辆)</t>
+          <t>🚨 交通拥堵警报！拥堵：20辆车，车速过慢 (1.2像素/帧)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10.33333333333333</v>
+        <v>27.3</v>
       </c>
       <c r="B11" t="n">
-        <v>310</v>
+        <v>819</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -756,29 +750,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>车辆过多 (22辆 &gt; 15辆)</t>
+          <t>拥堵：20辆车，车速过慢 (1.2像素/帧)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>1.221892222993487</v>
+        <v>1.161667273601693</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (22辆 &gt; 15辆)</t>
+          <t>🚨 交通拥堵警报！拥堵：20辆车，车速过慢 (1.2像素/帧)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11.36666666666667</v>
+        <v>30.33333333333333</v>
       </c>
       <c r="B12" t="n">
-        <v>341</v>
+        <v>910</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -787,578 +781,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>车辆过多 (20辆 &gt; 15辆)</t>
+          <t>拥堵：22辆车，车速过慢 (1.5像素/帧)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F12" t="n">
-        <v>1.301584231145171</v>
+        <v>1.516058403801706</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="B13" t="n">
-        <v>372</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>车辆过多 (18辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.310903114465476</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (18辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13.43333333333333</v>
-      </c>
-      <c r="B14" t="n">
-        <v>403</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>20</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.697044690451563</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14.46666666666667</v>
-      </c>
-      <c r="B15" t="n">
-        <v>434</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>车辆过多 (23辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>23</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.9775021005488934</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (23辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="B16" t="n">
-        <v>465</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>车辆过多 (21辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>21</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.033736122357235</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (21辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16.53333333333333</v>
-      </c>
-      <c r="B17" t="n">
-        <v>496</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>20</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.175378549108738</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17.56666666666667</v>
-      </c>
-      <c r="B18" t="n">
-        <v>527</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>车辆过多 (24辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>24</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1.787456947240474</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (24辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="B19" t="n">
-        <v>558</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>20</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.294099590819969</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19.63333333333333</v>
-      </c>
-      <c r="B20" t="n">
-        <v>589</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>20</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.568866452416513</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20.66666666666667</v>
-      </c>
-      <c r="B21" t="n">
-        <v>620</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>车辆过多 (22辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>22</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1.322822464017374</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (22辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="B22" t="n">
-        <v>651</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>车辆过多 (24辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>24</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.492512345908085</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (24辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22.73333333333333</v>
-      </c>
-      <c r="B23" t="n">
-        <v>682</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>车辆过多 (22辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>22</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.205101704255489</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (22辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23.76666666666667</v>
-      </c>
-      <c r="B24" t="n">
-        <v>713</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>20</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.301123650091493</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (20辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="B25" t="n">
-        <v>744</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>车辆过多 (21辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>21</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1.312835300681983</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (21辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25.83333333333333</v>
-      </c>
-      <c r="B26" t="n">
-        <v>775</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>车辆过多 (22辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>22</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.676700338206791</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (22辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26.86666666666667</v>
-      </c>
-      <c r="B27" t="n">
-        <v>806</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>车辆过多 (18辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>18</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1.165725752929761</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (18辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="B28" t="n">
-        <v>837</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>车辆过多 (22辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>22</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.043817729038984</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (22辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28.93333333333333</v>
-      </c>
-      <c r="B29" t="n">
-        <v>868</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>车辆过多 (18辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>18</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.97213741680312</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (18辆 &gt; 15辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29.96666666666667</v>
-      </c>
-      <c r="B30" t="n">
-        <v>899</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>congestion</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>车辆过多 (22辆 &gt; 15辆)</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>22</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.494287808946423</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>⚠️ 交通拥堵警报！车辆过多 (22辆 &gt; 15辆)</t>
+          <t>🚨 交通拥堵警报！拥堵：22辆车，车速过慢 (1.5像素/帧)</t>
         </is>
       </c>
     </row>
